--- a/app/data/table_short_labels.xlsx
+++ b/app/data/table_short_labels.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
   <si>
     <t xml:space="preserve">dataset</t>
   </si>
@@ -251,12 +251,6 @@
     <t xml:space="preserve">Canada - Permanent Residents by Province/Territory, Census Division and Census Subdivision</t>
   </si>
   <si>
-    <t xml:space="preserve">permanent_residents/166ea45e__canada_permanent_resident_by_province_territory_and_immigrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Permanent resident by province/territory and immigration category</t>
-  </si>
-  <si>
     <t xml:space="preserve">permanent_residents/bf9210c3__canada_ex_qc_admissions_of_french_speaking_permanent_residen</t>
   </si>
   <si>
@@ -326,12 +320,6 @@
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Province/Territory and Census Metropolitan Area — Pr Cma</t>
   </si>
   <si>
-    <t xml:space="preserve">permanent_residents/d034c26c__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_pt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Province/Territory and Census Metropolitan Area — Pr Pt</t>
-  </si>
-  <si>
     <t xml:space="preserve">permanent_residents/d034c26c__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_pt_cma</t>
   </si>
   <si>
@@ -344,12 +332,6 @@
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Province/Territory and Gender — Pr Gender</t>
   </si>
   <si>
-    <t xml:space="preserve">permanent_residents/f257263f__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_pt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Province/Territory and Gender — Pr Pt</t>
-  </si>
-  <si>
     <t xml:space="preserve">permanent_residents/f257263f__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_pt_gender</t>
   </si>
   <si>
@@ -374,12 +356,6 @@
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Province/Territory and Immigration Category — Pr Immcat m</t>
   </si>
   <si>
-    <t xml:space="preserve">permanent_residents/d839c522__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_pt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Province/Territory and Immigration Category — Pr Pt</t>
-  </si>
-  <si>
     <t xml:space="preserve">permanent_residents/d839c522__canada_ex_qc_french_speaking_permanent_residents_by_province__pr_pt_immcat</t>
   </si>
   <si>
@@ -504,12 +480,6 @@
   </si>
   <si>
     <t xml:space="preserve">By P/T, gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">study_permit_holders/3d1e30f5__canada_study_permit_holders_by_province_territory_study_leve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Study permit holders by province/territory, study level and year in which permit(s) became effective</t>
   </si>
   <si>
     <t xml:space="preserve">study_permit_holders/3897ef92__canada_study_permit_holders_on_december_31st_by_country_of_c</t>
@@ -800,8 +770,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D91" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D86" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D86"/>
   <tableColumns count="4">
     <tableColumn id="1" name="dataset"/>
     <tableColumn id="2" name="table_id"/>
@@ -1475,7 +1445,7 @@
         <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
@@ -1483,13 +1453,13 @@
         <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29">
@@ -1497,13 +1467,13 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
@@ -1511,13 +1481,13 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
@@ -1525,13 +1495,13 @@
         <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32">
@@ -1539,13 +1509,13 @@
         <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
@@ -1587,7 +1557,7 @@
         <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
@@ -1615,7 +1585,7 @@
         <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
@@ -1629,7 +1599,7 @@
         <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
@@ -1643,7 +1613,7 @@
         <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
@@ -1657,7 +1627,7 @@
         <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41">
@@ -1671,7 +1641,7 @@
         <v>113</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
@@ -1699,7 +1669,7 @@
         <v>117</v>
       </c>
       <c r="D43" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44">
@@ -1713,7 +1683,7 @@
         <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45">
@@ -1727,7 +1697,7 @@
         <v>121</v>
       </c>
       <c r="D45" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46">
@@ -1741,637 +1711,567 @@
         <v>123</v>
       </c>
       <c r="D46" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D48" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C53" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D55" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D56" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D57" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C62" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D62" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B64" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B65" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D65" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B66" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C66" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B67" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C67" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B68" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C68" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D68" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B69" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C69" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D69" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C70" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D70" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B71" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D71" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B72" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C72" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D72" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B73" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D73" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D74" t="s">
-        <v>200</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B75" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C75" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D76" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B77" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C77" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D77" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C78" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D78" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B79" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C79" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D79" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B80" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C80" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D80" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B81" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C81" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D81" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D82" t="s">
-        <v>186</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B83" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C83" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D83" t="s">
-        <v>189</v>
+        <v>227</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B84" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C84" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D84" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B85" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C85" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D85" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B86" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C86" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D86" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>220</v>
-      </c>
-      <c r="B87" t="s">
-        <v>232</v>
-      </c>
-      <c r="C87" t="s">
-        <v>233</v>
-      </c>
-      <c r="D87" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>234</v>
-      </c>
-      <c r="B88" t="s">
-        <v>235</v>
-      </c>
-      <c r="C88" t="s">
         <v>236</v>
-      </c>
-      <c r="D88" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>234</v>
-      </c>
-      <c r="B89" t="s">
-        <v>238</v>
-      </c>
-      <c r="C89" t="s">
-        <v>239</v>
-      </c>
-      <c r="D89" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>234</v>
-      </c>
-      <c r="B90" t="s">
-        <v>241</v>
-      </c>
-      <c r="C90" t="s">
-        <v>242</v>
-      </c>
-      <c r="D90" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>234</v>
-      </c>
-      <c r="B91" t="s">
-        <v>244</v>
-      </c>
-      <c r="C91" t="s">
-        <v>245</v>
-      </c>
-      <c r="D91" t="s">
-        <v>246</v>
       </c>
     </row>
   </sheetData>
